--- a/data/trans_orig/P32A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,47 +768,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>285143</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125079</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>412224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214033</t>
+          <t>215311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222240</t>
+          <t>222254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153862</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368788</t>
+          <t>368733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376117</t>
+          <t>376103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328231</t>
+          <t>328200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337059</t>
+          <t>337021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389562</t>
+          <t>390274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>652495</t>
+          <t>650733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>664866</t>
+          <t>665013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190341</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>844220</t>
+          <t>844620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857844</t>
+          <t>857209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209096</t>
+          <t>208951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133648</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346465</t>
+          <t>346647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355438</t>
+          <t>355485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4113</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6284</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5068</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213987</t>
+          <t>213028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>352543</t>
+          <t>351327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30712</t>
+          <t>31305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>34156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1846196</t>
+          <t>1845603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1863993</t>
+          <t>1864365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>885575</t>
+          <t>885511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>892575</t>
+          <t>892579</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2735230</t>
+          <t>2736251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2755402</t>
+          <t>2755656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280901</t>
+          <t>281776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290815</t>
+          <t>291465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141918</t>
+          <t>142388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>427290</t>
+          <t>426605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437574</t>
+          <t>437601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239433</t>
+          <t>239980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252536</t>
+          <t>252515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136766</t>
+          <t>134029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381762</t>
+          <t>381143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394133</t>
+          <t>394771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362642</t>
+          <t>363938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380209</t>
+          <t>380718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79548</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>443091</t>
+          <t>442813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>460076</t>
+          <t>459932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>28705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>633803</t>
+          <t>633437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650761</t>
+          <t>650785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>223369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>861340</t>
+          <t>860434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878908</t>
+          <t>878715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287519</t>
+          <t>286653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299130</t>
+          <t>298273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174736</t>
+          <t>175419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467883</t>
+          <t>467081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>480041</t>
+          <t>480043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127815</t>
+          <t>128553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>136355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251487</t>
+          <t>251688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384936</t>
+          <t>382502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396793</t>
+          <t>396729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67996</t>
+          <t>71007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45064</t>
+          <t>45245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78668</t>
+          <t>78165</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1966445</t>
+          <t>1963434</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1995668</t>
+          <t>1996155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1024931</t>
+          <t>1026541</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1039397</t>
+          <t>1039341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2999194</t>
+          <t>2999697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3032798</t>
+          <t>3032617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280611</t>
+          <t>280717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287823</t>
+          <t>287829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142413</t>
+          <t>143900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428278</t>
+          <t>428156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439868</t>
+          <t>439847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230763</t>
+          <t>230889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238090</t>
+          <t>238116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180642</t>
+          <t>180898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>190299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416556</t>
+          <t>415316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427453</t>
+          <t>427282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317269</t>
+          <t>317825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329284</t>
+          <t>329096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>49225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371193</t>
+          <t>370968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383554</t>
+          <t>383421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21036</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638140</t>
+          <t>637536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>652187</t>
+          <t>652256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292560</t>
+          <t>291766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>934052</t>
+          <t>934179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>948632</t>
+          <t>949294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296950</t>
+          <t>296212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>310969</t>
+          <t>310896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184980</t>
+          <t>186061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>486431</t>
+          <t>486438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>500982</t>
+          <t>500915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17266</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151672</t>
+          <t>151069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159987</t>
+          <t>159882</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242742</t>
+          <t>243165</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252782</t>
+          <t>252799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398328</t>
+          <t>398424</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>410770</t>
+          <t>410831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54415</t>
+          <t>54432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>42714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71154</t>
+          <t>72907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1940922</t>
+          <t>1940905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1967534</t>
+          <t>1966811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1116737</t>
+          <t>1116509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1133747</t>
+          <t>1133374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3066561</t>
+          <t>3064808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3096155</t>
+          <t>3095001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268287</t>
+          <t>269353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277805</t>
+          <t>278006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152597</t>
+          <t>151937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157621</t>
+          <t>157974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>424651</t>
+          <t>425017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434596</t>
+          <t>434979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,77 +9001,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>4475</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>9234</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2724</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6304</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>4475</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>9055</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205971</t>
+          <t>205659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211493</t>
+          <t>211495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,82 +9109,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>129116</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>124624</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>130849</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>339027</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>334268</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>341578</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>97,31%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>129116</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>125536</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>130864</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>339027</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>334447</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>341624</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201171</t>
+          <t>202014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209691</t>
+          <t>209711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242289</t>
+          <t>242860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250080</t>
+          <t>250071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>19806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487532</t>
+          <t>488494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>502211</t>
+          <t>501762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>403920</t>
+          <t>404615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412341</t>
+          <t>412400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>896029</t>
+          <t>896246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>914419</t>
+          <t>914666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220786</t>
+          <t>220286</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228937</t>
+          <t>229061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125446</t>
+          <t>125648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130248</t>
+          <t>130262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349118</t>
+          <t>349324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358206</t>
+          <t>357913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -10353,97 +10353,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11404</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2228</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10555</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11196</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205066</t>
+          <t>205707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>37775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54499</t>
+          <t>53868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1497840</t>
+          <t>1499678</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1518425</t>
+          <t>1518304</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>973972</t>
+          <t>973101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>989747</t>
+          <t>989539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2478343</t>
+          <t>2478974</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2506398</t>
+          <t>2505424</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285143</t>
+          <t>284735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>412224</t>
+          <t>412871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215311</t>
+          <t>214452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222254</t>
+          <t>222238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368733</t>
+          <t>368751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376103</t>
+          <t>376111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328200</t>
+          <t>328494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337021</t>
+          <t>337015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390274</t>
+          <t>390434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398780</t>
+          <t>398757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>650733</t>
+          <t>652147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665013</t>
+          <t>664929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>844620</t>
+          <t>844135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857209</t>
+          <t>857212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>208951</t>
+          <t>209527</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134369</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346647</t>
+          <t>347013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355485</t>
+          <t>355475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213028</t>
+          <t>211305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351327</t>
+          <t>351455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34156</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1845603</t>
+          <t>1845402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1864365</t>
+          <t>1864242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>885511</t>
+          <t>885493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>892579</t>
+          <t>892575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2736251</t>
+          <t>2735492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2755656</t>
+          <t>2755464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281776</t>
+          <t>281550</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291465</t>
+          <t>291523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>142055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426605</t>
+          <t>425655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437601</t>
+          <t>436897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239980</t>
+          <t>239381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252515</t>
+          <t>252527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134029</t>
+          <t>137683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381143</t>
+          <t>379293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394771</t>
+          <t>394083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>363938</t>
+          <t>362515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380718</t>
+          <t>380335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>442813</t>
+          <t>442701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459932</t>
+          <t>459820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26430</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>633437</t>
+          <t>634830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650785</t>
+          <t>650906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223369</t>
+          <t>223026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>860434</t>
+          <t>860845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878715</t>
+          <t>878479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286653</t>
+          <t>285867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>298273</t>
+          <t>298464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175419</t>
+          <t>175789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467081</t>
+          <t>467484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>480043</t>
+          <t>480634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128553</t>
+          <t>128671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136355</t>
+          <t>136408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251688</t>
+          <t>251853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382502</t>
+          <t>385202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396729</t>
+          <t>396661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>38881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71007</t>
+          <t>70228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45245</t>
+          <t>46166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78165</t>
+          <t>79157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1963434</t>
+          <t>1964213</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1996155</t>
+          <t>1995560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1026541</t>
+          <t>1025595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1039341</t>
+          <t>1040001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2999697</t>
+          <t>2998705</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3032617</t>
+          <t>3031696</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280717</t>
+          <t>278975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287829</t>
+          <t>287825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143900</t>
+          <t>143219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428156</t>
+          <t>428854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230889</t>
+          <t>230379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238116</t>
+          <t>238099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180898</t>
+          <t>180340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190299</t>
+          <t>190314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415316</t>
+          <t>414996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427282</t>
+          <t>427380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317825</t>
+          <t>316830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329096</t>
+          <t>329050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49225</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>370968</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383421</t>
+          <t>383360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637536</t>
+          <t>636426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>652256</t>
+          <t>652031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291766</t>
+          <t>290584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>934179</t>
+          <t>933632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>949294</t>
+          <t>948742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296212</t>
+          <t>297331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>310896</t>
+          <t>311114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186061</t>
+          <t>185406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>486438</t>
+          <t>485817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>500915</t>
+          <t>501103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151069</t>
+          <t>151085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159882</t>
+          <t>159879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243165</t>
+          <t>243443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252799</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398424</t>
+          <t>398916</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>410831</t>
+          <t>411016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>53575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42714</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72907</t>
+          <t>72436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1940905</t>
+          <t>1941762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1966811</t>
+          <t>1967235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1116509</t>
+          <t>1116256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1133374</t>
+          <t>1133281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3064808</t>
+          <t>3065279</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3095001</t>
+          <t>3096588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>274926</t>
+          <t>294710</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269353</t>
+          <t>287668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278006</t>
+          <t>298178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155905</t>
+          <t>168477</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151937</t>
+          <t>164637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157974</t>
+          <t>170219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>430831</t>
+          <t>463186</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425017</t>
+          <t>456300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434979</t>
+          <t>467477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>209911</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>216073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211495</t>
+          <t>222679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>129116</t>
+          <t>139521</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124624</t>
+          <t>135008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130849</t>
+          <t>142021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>339027</t>
+          <t>360309</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334268</t>
+          <t>354849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341578</t>
+          <t>363852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>143571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>143571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>143571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>343502</t>
+          <t>366933</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>343502</t>
+          <t>366933</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>343502</t>
+          <t>366933</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>207080</t>
+          <t>223958</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202014</t>
+          <t>218906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209711</t>
+          <t>226543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>247413</t>
+          <t>270523</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242860</t>
+          <t>265656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250071</t>
+          <t>273077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>496759</t>
+          <t>528810</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488494</t>
+          <t>520026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501762</t>
+          <t>534545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>409740</t>
+          <t>221684</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404615</t>
+          <t>212006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412400</t>
+          <t>225906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>906499</t>
+          <t>750494</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>896246</t>
+          <t>738650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>914666</t>
+          <t>757659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>412580</t>
+          <t>228209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>412580</t>
+          <t>228209</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>412580</t>
+          <t>228209</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>920880</t>
+          <t>768480</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>920880</t>
+          <t>768480</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>920880</t>
+          <t>768480</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>226089</t>
+          <t>251971</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220286</t>
+          <t>246862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229061</t>
+          <t>254846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128633</t>
+          <t>150641</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125648</t>
+          <t>147475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130262</t>
+          <t>152221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>354724</t>
+          <t>402612</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349324</t>
+          <t>397635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357913</t>
+          <t>406287</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>214034</t>
+          <t>210088</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205707</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>29561</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>40909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>47245</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53868</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10804,17 +10804,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1509626</t>
+          <t>1606079</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1499678</t>
+          <t>1594731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1518304</t>
+          <t>1615620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>982903</t>
+          <t>851134</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>973101</t>
+          <t>840370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>989539</t>
+          <t>858336</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2492528</t>
+          <t>2457213</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2478974</t>
+          <t>2441574</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2505424</t>
+          <t>2468831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>995389</t>
+          <t>868818</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>995389</t>
+          <t>868818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>995389</t>
+          <t>868818</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2532842</t>
+          <t>2504458</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2532842</t>
+          <t>2504458</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2532842</t>
+          <t>2504458</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
